--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -2845,7 +2845,7 @@
         <v>136444071</v>
       </c>
       <c r="B20" t="n">
-        <v>56873</v>
+        <v>56875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136444067</v>
       </c>
       <c r="B21" t="n">
-        <v>56864</v>
+        <v>56866</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
